--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Surveys\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3A5970-46B2-41D0-9FC0-B30B40D2478D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4088853D-E686-418E-959B-29D411FF8FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="23">
   <si>
     <t>Vessel</t>
   </si>
@@ -121,6 +121,15 @@
   </si>
   <si>
     <t>*Use to randomly select. Change number to whatever number of vessels are participating. Copy and paste value into above chart.</t>
+  </si>
+  <si>
+    <t>SB9</t>
+  </si>
+  <si>
+    <t>SB10</t>
+  </si>
+  <si>
+    <t>SB11</t>
   </si>
 </sst>
 </file>
@@ -523,10 +532,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0E4B6A-B7B4-44A9-982B-5336CC10E260}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -539,7 +548,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,8 +576,17 @@
       <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -590,8 +608,12 @@
       <c r="G3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -613,8 +635,12 @@
       <c r="G4" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -636,8 +662,12 @@
       <c r="G5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -659,8 +689,12 @@
       <c r="G6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -682,8 +716,12 @@
       <c r="G7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -705,8 +743,11 @@
       <c r="G8">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -719,7 +760,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -748,93 +789,105 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B13" s="3"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B23" cm="1">
         <f t="array" aca="1" ref="B23:B28" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(6), _xlfn.RANDARRAY(6))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B27">
         <f ca="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
@@ -843,7 +896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>17</v>
       </c>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Surveys\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4088853D-E686-418E-959B-29D411FF8FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2555F6-A4A4-4D33-8402-E8B4F53E87D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="1290" yWindow="765" windowWidth="24675" windowHeight="12300" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
   <si>
     <t>Vessel</t>
   </si>
@@ -130,6 +130,30 @@
   </si>
   <si>
     <t>SB11</t>
+  </si>
+  <si>
+    <t>GB1</t>
+  </si>
+  <si>
+    <t>GB2</t>
+  </si>
+  <si>
+    <t>GB3</t>
+  </si>
+  <si>
+    <t>GB4</t>
+  </si>
+  <si>
+    <t>GB5</t>
+  </si>
+  <si>
+    <t>GB6</t>
+  </si>
+  <si>
+    <t>GB7</t>
+  </si>
+  <si>
+    <t>GB8</t>
   </si>
 </sst>
 </file>
@@ -191,12 +215,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -765,120 +795,177 @@
         <v>0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="B13" s="3">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="B14" s="4">
+        <v>2</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="B15" s="4">
+        <v>6</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="4">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
+        <v>7</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="4">
+        <v>4</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" aca="1" ref="B23:B28" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(6), _xlfn.RANDARRAY(6))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="B23:B29" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(7), _xlfn.RANDARRAY(7))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
@@ -887,18 +974,22 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B28">
         <f ca="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="B29">
+        <f ca="1"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Surveys\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2555F6-A4A4-4D33-8402-E8B4F53E87D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD194FC-ACBE-49A7-808C-3622AB56E0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="765" windowWidth="24675" windowHeight="12300" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -722,7 +722,7 @@
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -749,7 +749,7 @@
       <c r="H7">
         <v>3</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -854,7 +854,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -869,10 +869,9 @@
         <v>4</v>
       </c>
       <c r="B16" s="4">
-        <v>5</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="D16" s="5"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -886,8 +885,7 @@
       <c r="B17" s="4">
         <v>1</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="5"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -899,7 +897,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -913,9 +911,7 @@
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="4">
-        <v>4</v>
-      </c>
+      <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -935,7 +931,7 @@
       </c>
       <c r="B23" cm="1">
         <f t="array" aca="1" ref="B23:B29" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(7), _xlfn.RANDARRAY(7))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -953,7 +949,7 @@
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -962,7 +958,7 @@
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -971,7 +967,7 @@
       </c>
       <c r="B27">
         <f ca="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -989,7 +985,7 @@
       </c>
       <c r="B29">
         <f ca="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Surveys\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD194FC-ACBE-49A7-808C-3622AB56E0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA535C39-E085-4AF2-88DB-8709E2A8B892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="1125" yWindow="990" windowWidth="24675" windowHeight="12300" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -641,6 +641,9 @@
       <c r="H3">
         <v>6</v>
       </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -668,6 +671,9 @@
       <c r="H4">
         <v>4</v>
       </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -695,6 +701,9 @@
       <c r="H5">
         <v>5</v>
       </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -722,6 +731,9 @@
       <c r="H6">
         <v>1</v>
       </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -749,7 +761,9 @@
       <c r="H7">
         <v>3</v>
       </c>
-      <c r="I7" s="2"/>
+      <c r="I7" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -775,6 +789,9 @@
       </c>
       <c r="H8" s="2">
         <v>2</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -826,7 +843,9 @@
       <c r="B13" s="3">
         <v>3</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="4">
+        <v>2</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="5"/>
@@ -841,7 +860,9 @@
       <c r="B14" s="4">
         <v>2</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="4">
+        <v>4</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="5"/>
@@ -856,7 +877,9 @@
       <c r="B15" s="4">
         <v>5</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
       <c r="F15" s="4"/>
@@ -871,6 +894,9 @@
       <c r="B16" s="4">
         <v>4</v>
       </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
       <c r="D16" s="5"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -885,7 +911,9 @@
       <c r="B17" s="4">
         <v>1</v>
       </c>
-      <c r="C17" s="5"/>
+      <c r="C17" s="5">
+        <v>6</v>
+      </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -899,7 +927,9 @@
       <c r="B18" s="5">
         <v>6</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="4">
+        <v>3</v>
+      </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -930,8 +960,8 @@
         <v>1</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" aca="1" ref="B23:B29" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(7), _xlfn.RANDARRAY(7))</f>
-        <v>2</v>
+        <f t="array" aca="1" ref="B23:B28" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(6), _xlfn.RANDARRAY(6))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -940,7 +970,7 @@
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -949,7 +979,7 @@
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -958,7 +988,7 @@
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -967,7 +997,7 @@
       </c>
       <c r="B27">
         <f ca="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -976,16 +1006,12 @@
       </c>
       <c r="B28">
         <f ca="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B29">
-        <f ca="1"/>
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Surveys\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA535C39-E085-4AF2-88DB-8709E2A8B892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="990" windowWidth="24675" windowHeight="12300" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
   <si>
     <t>Vessel</t>
   </si>
@@ -154,6 +154,15 @@
   </si>
   <si>
     <t>GB8</t>
+  </si>
+  <si>
+    <t>(1)</t>
+  </si>
+  <si>
+    <t>Any number in () = they originally were scheduled but had to drop last minute.</t>
+  </si>
+  <si>
+    <t>(5)</t>
   </si>
 </sst>
 </file>
@@ -215,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -228,6 +237,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -698,8 +711,8 @@
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5">
-        <v>5</v>
+      <c r="H5" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -732,7 +745,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J6" s="2"/>
     </row>
@@ -791,7 +804,7 @@
         <v>2</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -799,7 +812,9 @@
         <v>16</v>
       </c>
       <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -908,8 +923,8 @@
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="4">
-        <v>1</v>
+      <c r="B17" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="C17" s="5">
         <v>6</v>
@@ -961,7 +976,7 @@
       </c>
       <c r="B23" cm="1">
         <f t="array" aca="1" ref="B23:B28" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(6), _xlfn.RANDARRAY(6))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -970,7 +985,7 @@
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -979,7 +994,7 @@
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1006,7 +1021,7 @@
       </c>
       <c r="B28">
         <f ca="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Surveys\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40E0E2B5-4425-4F9F-BCF1-1D68622E7F20}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="4410" yWindow="3030" windowWidth="21600" windowHeight="11300" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
   <si>
     <t>Vessel</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <t>(5)</t>
+  </si>
+  <si>
+    <t>(3)</t>
+  </si>
+  <si>
+    <t>(2)</t>
   </si>
 </sst>
 </file>
@@ -224,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -241,6 +247,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,9 +586,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0E4B6A-B7B4-44A9-982B-5336CC10E260}">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -591,7 +601,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,7 +639,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -659,7 +669,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -689,7 +699,7 @@
       </c>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -714,12 +724,12 @@
       <c r="H5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>5</v>
       </c>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -744,12 +754,12 @@
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6">
-        <v>3</v>
+      <c r="I6" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -774,11 +784,11 @@
       <c r="H7">
         <v>3</v>
       </c>
-      <c r="I7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I7" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -807,7 +817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -822,7 +832,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -851,7 +861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -859,7 +869,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -868,7 +878,7 @@
       <c r="H13" s="5"/>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>2</v>
       </c>
@@ -876,7 +886,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -885,15 +895,15 @@
       <c r="H14" s="5"/>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="4">
         <v>5</v>
       </c>
-      <c r="C15" s="4">
-        <v>1</v>
+      <c r="C15" s="5">
+        <v>7</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
@@ -902,7 +912,7 @@
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -910,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="4"/>
@@ -919,15 +929,15 @@
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="5">
-        <v>6</v>
+      <c r="C17" s="9">
+        <v>4</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -935,7 +945,7 @@
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -943,7 +953,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -952,12 +962,14 @@
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -965,68 +977,72 @@
       <c r="H19" s="5"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" aca="1" ref="B23:B28" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(6), _xlfn.RANDARRAY(6))</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="B23:B29" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(7), _xlfn.RANDARRAY(7))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B27">
         <f ca="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B28">
         <f ca="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="B29">
+        <f ca="1"/>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40E0E2B5-4425-4F9F-BCF1-1D68622E7F20}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7625EA63-EB54-4F8B-9E05-C8D5572BBAD2}"/>
   <bookViews>
-    <workbookView xWindow="4410" yWindow="3030" windowWidth="21600" windowHeight="11300" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="2110" yWindow="1850" windowWidth="34910" windowHeight="17240" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -251,6 +251,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,7 +668,11 @@
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="L3" s="2"/>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -697,7 +702,11 @@
       <c r="I4">
         <v>4</v>
       </c>
-      <c r="L4" s="2"/>
+      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -727,7 +736,11 @@
       <c r="I5" s="2">
         <v>5</v>
       </c>
-      <c r="K5" s="2"/>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
@@ -757,7 +770,8 @@
       <c r="I6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -787,6 +801,11 @@
       <c r="I7" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="J7" s="2">
+        <v>2</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
@@ -816,6 +835,8 @@
       <c r="I8">
         <v>6</v>
       </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
@@ -871,12 +892,14 @@
       <c r="C13" s="4">
         <v>6</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="4"/>
+      <c r="D13" s="4">
+        <v>5</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -888,12 +911,14 @@
       <c r="C14" s="4">
         <v>5</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="4"/>
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
@@ -902,15 +927,17 @@
       <c r="B15" s="4">
         <v>5</v>
       </c>
-      <c r="C15" s="5">
-        <v>7</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="C15" s="9">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
@@ -919,15 +946,17 @@
       <c r="B16" s="4">
         <v>4</v>
       </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="C16" s="2">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
@@ -936,14 +965,17 @@
       <c r="B17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="9">
-        <v>4</v>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
+      <c r="C17" s="4">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>7</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
@@ -955,12 +987,14 @@
       <c r="C18" s="4">
         <v>2</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
+      <c r="D18" s="4">
+        <v>4</v>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -970,12 +1004,21 @@
       <c r="C19" s="4">
         <v>1</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="4"/>
+      <c r="D19" s="4">
+        <v>6</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
@@ -987,8 +1030,8 @@
         <v>1</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" aca="1" ref="B23:B29" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(7), _xlfn.RANDARRAY(7))</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="B23:B26" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(4), _xlfn.RANDARRAY(4))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -997,7 +1040,7 @@
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1006,7 +1049,7 @@
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1015,34 +1058,22 @@
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B27">
-        <f ca="1"/>
-        <v>6</v>
-      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B28">
-        <f ca="1"/>
-        <v>3</v>
-      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B29">
-        <f ca="1"/>
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7625EA63-EB54-4F8B-9E05-C8D5572BBAD2}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FC1421C-BF37-4142-99B9-81120718A932}"/>
   <bookViews>
-    <workbookView xWindow="2110" yWindow="1850" windowWidth="34910" windowHeight="17240" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="1695" yWindow="120" windowWidth="28800" windowHeight="15450" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -248,10 +248,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,9 +583,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0E4B6A-B7B4-44A9-982B-5336CC10E260}">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -602,7 +598,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -640,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -668,13 +664,8 @@
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -703,12 +694,10 @@
         <v>4</v>
       </c>
       <c r="J4">
-        <v>4</v>
-      </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -736,13 +725,8 @@
       <c r="I5" s="2">
         <v>5</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -770,10 +754,11 @@
       <c r="I6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -804,10 +789,8 @@
       <c r="J7" s="2">
         <v>2</v>
       </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,10 +818,8 @@
       <c r="I8">
         <v>6</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -853,7 +834,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -882,7 +863,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -895,13 +876,13 @@
       <c r="D13" s="4">
         <v>5</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>2</v>
       </c>
@@ -914,32 +895,32 @@
       <c r="D14" s="4">
         <v>3</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="4">
         <v>5</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="4">
         <v>3</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -952,13 +933,13 @@
       <c r="D16">
         <v>2</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -971,13 +952,13 @@
       <c r="D17" s="5">
         <v>7</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -990,13 +971,13 @@
       <c r="D18" s="4">
         <v>4</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1007,52 +988,45 @@
       <c r="D19" s="4">
         <v>6</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B23" cm="1">
         <f t="array" aca="1" ref="B23:B26" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(4), _xlfn.RANDARRAY(4))</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
@@ -1061,17 +1035,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>17</v>
       </c>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FC1421C-BF37-4142-99B9-81120718A932}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C8A8A43-23CA-46BE-ABE5-6DC26A1F3DE0}"/>
   <bookViews>
-    <workbookView xWindow="1695" yWindow="120" windowWidth="28800" windowHeight="15450" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -583,9 +583,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0E4B6A-B7B4-44A9-982B-5336CC10E260}">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -598,7 +598,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -665,7 +665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -726,7 +726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -790,7 +790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -819,7 +819,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -834,7 +834,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -863,7 +863,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -882,7 +882,7 @@
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>2</v>
       </c>
@@ -901,7 +901,7 @@
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
@@ -920,7 +920,7 @@
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -939,7 +939,7 @@
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -958,7 +958,7 @@
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -977,7 +977,7 @@
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -994,60 +994,72 @@
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" aca="1" ref="B23:B26" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(4), _xlfn.RANDARRAY(4))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="B23:B29" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(7), _xlfn.RANDARRAY(7))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <f ca="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="B29">
+        <f ca="1"/>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C8A8A43-23CA-46BE-ABE5-6DC26A1F3DE0}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBD84B37-1F46-4C4D-BCCF-942278997624}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -893,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -950,7 +950,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B29">
         <f ca="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBD84B37-1F46-4C4D-BCCF-942278997624}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41DF781E-3BAF-4A5C-85DB-7935F97FBAED}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="-38510" yWindow="-20" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
   <si>
     <t>Vessel</t>
   </si>
@@ -169,6 +169,24 @@
   </si>
   <si>
     <t>(2)</t>
+  </si>
+  <si>
+    <t>*7</t>
+  </si>
+  <si>
+    <t>Green with * was the plankton vessel, green without star was supposed to be but had a reason they couldn't.</t>
+  </si>
+  <si>
+    <t>*6</t>
+  </si>
+  <si>
+    <t>*1</t>
+  </si>
+  <si>
+    <t>*2</t>
+  </si>
+  <si>
+    <t>*5</t>
   </si>
 </sst>
 </file>
@@ -590,7 +608,9 @@
         <v>15</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -640,17 +660,17 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
+      <c r="B3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -663,6 +683,9 @@
       </c>
       <c r="I3">
         <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -681,11 +704,11 @@
       <c r="E4">
         <v>5</v>
       </c>
-      <c r="F4" s="2">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2">
-        <v>2</v>
+      <c r="F4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -693,8 +716,8 @@
       <c r="I4">
         <v>4</v>
       </c>
-      <c r="J4">
-        <v>3</v>
+      <c r="J4" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -722,8 +745,11 @@
       <c r="H5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="2">
-        <v>5</v>
+      <c r="I5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -786,8 +812,8 @@
       <c r="I7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="2">
-        <v>2</v>
+      <c r="J7" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -812,11 +838,14 @@
       <c r="G8">
         <v>6</v>
       </c>
-      <c r="H8" s="2">
-        <v>2</v>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="I8">
         <v>6</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -892,8 +921,8 @@
       <c r="C14" s="4">
         <v>5</v>
       </c>
-      <c r="D14" s="4">
-        <v>7</v>
+      <c r="D14" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -927,8 +956,8 @@
       <c r="B16" s="4">
         <v>4</v>
       </c>
-      <c r="C16" s="2">
-        <v>7</v>
+      <c r="C16" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -962,8 +991,8 @@
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="5">
-        <v>6</v>
+      <c r="B18" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C18" s="4">
         <v>2</v>
@@ -985,7 +1014,7 @@
       <c r="C19" s="4">
         <v>1</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <v>6</v>
       </c>
       <c r="E19" s="4"/>
@@ -1004,8 +1033,8 @@
         <v>1</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" aca="1" ref="B23:B29" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(7), _xlfn.RANDARRAY(7))</f>
-        <v>3</v>
+        <f t="array" aca="1" ref="B23:B25" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(3), _xlfn.RANDARRAY(3))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1014,7 +1043,7 @@
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1023,43 +1052,27 @@
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B26">
-        <f ca="1"/>
-        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B27">
-        <f ca="1"/>
-        <v>2</v>
-      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B28">
-        <f ca="1"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B29">
-        <f ca="1"/>
-        <v>5</v>
       </c>
     </row>
   </sheetData>
